--- a/public/kk-gabnaeyeokseo.xlsx
+++ b/public/kk-gabnaeyeokseo.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAB93FB-9966-E04B-B892-D8E2935BACA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="3280" windowWidth="38400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="3280" windowWidth="38400" windowHeight="19120"/>
   </bookViews>
   <sheets>
-    <sheet name="양식" sheetId="1" r:id="rId1"/>
-    <sheet name="필드" sheetId="2" r:id="rId2"/>
-    <sheet name="안내" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="양식" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="필드" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="안내" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -121,7 +120,7 @@
     <t>주의사항</t>
   </si>
   <si>
-    <t>* 기본 PET도어 / 무몰딩형 기준으로 견적 - 추후 디자인 및 부속의 변경, 추가에 따라 추가금이 발생합니다.
+    <t xml:space="preserve">* 기본 PET도어 / 무몰딩형 기준으로 견적 - 추후 디자인 및 부속의 변경, 추가에 따라 추가금이 발생합니다.
 * 공사 진행시 엘리베이터 사용료 또는 공사보증금, 보양비, 철거 비용 발생시 별도 진행됩니다.
 * 현장 상황에 따라 철거가 발생할 경우 품목에 따라 기본비 130,000 + α 가 발생됩니다.
 * 가구의 모든 몸통은 SE0 등급 기준입니다.(단, 자재 수급에 따라 변동될 수 있습니다)
@@ -285,136 +284,127 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="129"/>
+      <color rgb="FF9CA1AD"/>
+      <family val="2"/>
       <sz val="9"/>
-      <color rgb="FF9CA1AD"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
       <b/>
+      <charset val="129"/>
+      <color rgb="FF16181C"/>
+      <family val="2"/>
       <sz val="26"/>
-      <color rgb="FF16181C"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
+      <charset val="129"/>
+      <color rgb="FF16181C"/>
+      <family val="2"/>
       <sz val="8"/>
-      <color rgb="FF16181C"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
       <b/>
+      <charset val="129"/>
+      <color rgb="FF9CA1AD"/>
+      <family val="2"/>
       <sz val="9"/>
-      <color rgb="FF9CA1AD"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
     </font>
     <font>
-      <sz val="14"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
     </font>
     <font>
+      <charset val="129"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <charset val="129"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="18"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="9"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="8"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
+      <color theme="0" tint="-0.249977111117893"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color theme="0" tint="-0.249977111117893"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <charset val="129"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="10"/>
-      <color theme="0" tint="-0.249977111117893"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <charset val="129"/>
+      <color rgb="FF9CA1AD"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="14"/>
-      <color rgb="FF9CA1AD"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
+    </font>
+    <font>
+      <color rgb="FF9CA1AD"/>
+      <sz val="9"/>
     </font>
     <font>
       <b/>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -426,7 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -623,8 +613,56 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -636,54 +674,6 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -694,8 +684,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -703,8 +699,149 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -725,164 +862,18 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1218,730 +1209,786 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="24" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AB60"/>
+  <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125" customHeight="1"/>
   <cols>
     <col min="1" max="24" width="4" customWidth="1"/>
     <col min="26" max="26" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="24" customHeight="1">
-      <c r="A1" s="44" t="s">
+    <row r="1" ht="24" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="45" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Z1" s="2" t="s">
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Z1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="24" customHeight="1">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-    </row>
-    <row r="3" spans="1:26" s="3" customFormat="1" ht="24" customHeight="1">
-      <c r="A3" s="46" t="s">
+    <row r="2" ht="24" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="48" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="47" t="s">
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="48" t="s">
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="W3" s="48"/>
-      <c r="X3" s="49"/>
-    </row>
-    <row r="4" spans="1:26" s="3" customFormat="1" ht="24" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="9"/>
+      <c r="Z3" s="5"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="37" t="s">
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="38" t="s">
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="39"/>
-    </row>
-    <row r="5" spans="1:26" s="3" customFormat="1" ht="24" customHeight="1">
-      <c r="A5" s="40" t="s">
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="13"/>
+      <c r="Z4" s="5"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="42" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="41" t="s">
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="42" t="s">
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="S5" s="42"/>
-      <c r="T5" s="42"/>
-      <c r="U5" s="42"/>
-      <c r="V5" s="42"/>
-      <c r="W5" s="42"/>
-      <c r="X5" s="43"/>
-    </row>
-    <row r="6" spans="1:26" s="3" customFormat="1" ht="24" customHeight="1">
-      <c r="A6" s="26" t="s">
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="17"/>
+      <c r="Z5" s="5"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="31" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="31"/>
-      <c r="R6" s="31"/>
-      <c r="S6" s="31"/>
-      <c r="T6" s="31"/>
-      <c r="U6" s="31"/>
-      <c r="V6" s="31"/>
-      <c r="W6" s="31"/>
-      <c r="X6" s="32"/>
-    </row>
-    <row r="7" spans="1:26" s="3" customFormat="1" ht="24" customHeight="1" thickBot="1"/>
-    <row r="8" spans="1:26" s="3" customFormat="1" ht="24" customHeight="1">
-      <c r="A8" s="33" t="s">
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="21"/>
+      <c r="Z6" s="5"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="26:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z7" s="5"/>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="17" t="s">
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="17" t="s">
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="34" t="s">
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="T8" s="34"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34"/>
-      <c r="W8" s="34"/>
-      <c r="X8" s="35"/>
-      <c r="Z8" s="3" t="s">
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="27"/>
+      <c r="Z8" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="4" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A9" s="50" t="s">
+    <row r="9" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="52" t="s">
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="55" t="s">
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="56"/>
-      <c r="P9" s="56"/>
-      <c r="Q9" s="56"/>
-      <c r="R9" s="57"/>
-      <c r="S9" s="58" t="s">
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="T9" s="59"/>
-      <c r="U9" s="59"/>
-      <c r="V9" s="59"/>
-      <c r="W9" s="59"/>
-      <c r="X9" s="60"/>
-      <c r="Z9" s="4" t="s">
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="38"/>
+      <c r="X9" s="39"/>
+      <c r="Z9" s="28" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A10" s="28" t="s">
+    <row r="10" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29" t="s">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="30"/>
-    </row>
-    <row r="11" spans="1:26" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A11" s="20" t="s">
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="41"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="41"/>
+      <c r="W10" s="41"/>
+      <c r="X10" s="42"/>
+      <c r="Z10" s="28"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="21" t="s">
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
-      <c r="V11" s="21"/>
-      <c r="W11" s="21"/>
-      <c r="X11" s="22"/>
-    </row>
-    <row r="12" spans="1:26" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A12" s="23" t="s">
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="44"/>
+      <c r="X11" s="45"/>
+      <c r="Z11" s="28"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24" t="s">
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
-      <c r="W12" s="24"/>
-      <c r="X12" s="63"/>
-    </row>
-    <row r="13" spans="1:26" s="4" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A13" s="61"/>
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
-      <c r="L13" s="62"/>
-      <c r="M13" s="62"/>
-      <c r="N13" s="62"/>
-      <c r="O13" s="62"/>
-      <c r="P13" s="62"/>
-      <c r="Q13" s="62"/>
-      <c r="R13" s="62"/>
-      <c r="S13" s="62"/>
-      <c r="T13" s="62"/>
-      <c r="U13" s="62"/>
-      <c r="V13" s="62"/>
-      <c r="W13" s="62"/>
-      <c r="X13" s="64"/>
-    </row>
-    <row r="14" spans="1:26" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A14" s="25" t="s">
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="47"/>
+      <c r="V12" s="47"/>
+      <c r="W12" s="47"/>
+      <c r="X12" s="48"/>
+      <c r="Z12" s="28"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="49"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="50"/>
+      <c r="U13" s="50"/>
+      <c r="V13" s="50"/>
+      <c r="W13" s="50"/>
+      <c r="X13" s="51"/>
+      <c r="Z13" s="28"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="25"/>
-      <c r="S14" s="25"/>
-      <c r="T14" s="25"/>
-      <c r="U14" s="25"/>
-      <c r="V14" s="25"/>
-      <c r="W14" s="25"/>
-      <c r="X14" s="25"/>
-    </row>
-    <row r="15" spans="1:26" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A15" s="16" t="s">
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="52"/>
+      <c r="O14" s="52"/>
+      <c r="P14" s="52"/>
+      <c r="Q14" s="52"/>
+      <c r="R14" s="52"/>
+      <c r="S14" s="52"/>
+      <c r="T14" s="52"/>
+      <c r="U14" s="52"/>
+      <c r="V14" s="52"/>
+      <c r="W14" s="52"/>
+      <c r="X14" s="52"/>
+      <c r="Z14" s="28"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-    </row>
-    <row r="16" spans="1:26" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-    </row>
-    <row r="17" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="AB17" s="5"/>
-    </row>
-    <row r="18" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="16"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-    </row>
-    <row r="19" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-    </row>
-    <row r="20" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
-    </row>
-    <row r="21" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A21" s="6"/>
-    </row>
-    <row r="22" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A22" s="6"/>
-    </row>
-    <row r="23" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A23" s="7"/>
-    </row>
-    <row r="24" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A24" s="6"/>
-    </row>
-    <row r="25" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
-      <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="8"/>
-      <c r="Z25" s="9"/>
-    </row>
-    <row r="26" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1"/>
-    <row r="27" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1"/>
-    <row r="28" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1"/>
-    <row r="29" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1"/>
-    <row r="30" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1"/>
-    <row r="31" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="Z31" s="10" t="s">
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="53"/>
+      <c r="P15" s="53"/>
+      <c r="Q15" s="53"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="53"/>
+      <c r="T15" s="53"/>
+      <c r="U15" s="53"/>
+      <c r="V15" s="53"/>
+      <c r="W15" s="53"/>
+      <c r="X15" s="53"/>
+      <c r="Z15" s="28"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="53"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="53"/>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="53"/>
+      <c r="T16" s="53"/>
+      <c r="U16" s="53"/>
+      <c r="V16" s="53"/>
+      <c r="W16" s="53"/>
+      <c r="X16" s="53"/>
+      <c r="Z16" s="28"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:28" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="53"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="53"/>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="53"/>
+      <c r="T17" s="53"/>
+      <c r="U17" s="53"/>
+      <c r="V17" s="53"/>
+      <c r="W17" s="53"/>
+      <c r="X17" s="53"/>
+      <c r="Z17" s="28"/>
+      <c r="AB17" s="54"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="53"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="53"/>
+      <c r="P18" s="53"/>
+      <c r="Q18" s="53"/>
+      <c r="R18" s="53"/>
+      <c r="S18" s="53"/>
+      <c r="T18" s="53"/>
+      <c r="U18" s="53"/>
+      <c r="V18" s="53"/>
+      <c r="W18" s="53"/>
+      <c r="X18" s="53"/>
+      <c r="Z18" s="28"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="53"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="53"/>
+      <c r="P19" s="53"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="53"/>
+      <c r="S19" s="53"/>
+      <c r="T19" s="53"/>
+      <c r="U19" s="53"/>
+      <c r="V19" s="53"/>
+      <c r="W19" s="53"/>
+      <c r="X19" s="53"/>
+      <c r="Z19" s="28"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="53"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="53"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="53"/>
+      <c r="T20" s="53"/>
+      <c r="U20" s="53"/>
+      <c r="V20" s="53"/>
+      <c r="W20" s="53"/>
+      <c r="X20" s="53"/>
+      <c r="Z20" s="28"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="55"/>
+      <c r="Z21" s="28"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="55"/>
+      <c r="Z22" s="28"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="56"/>
+      <c r="Z23" s="28"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="55"/>
+      <c r="Z24" s="28"/>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="57"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="57"/>
+      <c r="P25" s="57"/>
+      <c r="Q25" s="57"/>
+      <c r="R25" s="57"/>
+      <c r="S25" s="57"/>
+      <c r="T25" s="57"/>
+      <c r="U25" s="57"/>
+      <c r="V25" s="57"/>
+      <c r="W25" s="57"/>
+      <c r="X25" s="57"/>
+      <c r="Z25" s="58"/>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="26:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z26" s="28"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="26:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z27" s="28"/>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="26:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z28" s="28"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="26:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z29" s="28"/>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="26:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z30" s="28"/>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="26:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z31" s="59"/>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="26:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z32" s="28"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="26:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z33" s="28"/>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="26:26" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z34" s="28"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
+      <c r="U35" s="28"/>
+      <c r="V35" s="28"/>
+      <c r="W35" s="28"/>
+      <c r="X35" s="28"/>
+      <c r="Z35" s="5"/>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="28"/>
+      <c r="T36" s="28"/>
+      <c r="U36" s="28"/>
+      <c r="V36" s="28"/>
+      <c r="W36" s="28"/>
+      <c r="X36" s="28"/>
+      <c r="Z36" s="5"/>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A37" s="57"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="57"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="57"/>
+      <c r="W37" s="57"/>
+      <c r="X37" s="57"/>
+      <c r="Z37" s="60"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z42" s="61" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:28" s="4" customFormat="1" ht="24" customHeight="1"/>
-    <row r="33" spans="1:26" s="4" customFormat="1" ht="24" customHeight="1"/>
-    <row r="34" spans="1:26" s="4" customFormat="1" ht="24" customHeight="1"/>
-    <row r="35" spans="1:26" s="3" customFormat="1" ht="24" customHeight="1">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
-    </row>
-    <row r="36" spans="1:26" s="3" customFormat="1" ht="24" customHeight="1">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
-    </row>
-    <row r="37" spans="1:26" ht="24" customHeight="1">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-      <c r="P37" s="8"/>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="8"/>
-      <c r="S37" s="8"/>
-      <c r="T37" s="8"/>
-      <c r="U37" s="8"/>
-      <c r="V37" s="8"/>
-      <c r="W37" s="8"/>
-      <c r="X37" s="8"/>
-      <c r="Z37" s="11"/>
-    </row>
+    <row r="43" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="26:26" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="N11:X11"/>
-    <mergeCell ref="A12:M13"/>
-    <mergeCell ref="N12:X13"/>
     <mergeCell ref="A1:E2"/>
     <mergeCell ref="F1:S2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:L3"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="R3:X3"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:X6"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="S8:X8"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="E4:L4"/>
     <mergeCell ref="M4:Q4"/>
@@ -1950,33 +1997,43 @@
     <mergeCell ref="E5:L5"/>
     <mergeCell ref="M5:Q5"/>
     <mergeCell ref="R5:X5"/>
-    <mergeCell ref="A15:X20"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:X6"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:M8"/>
+    <mergeCell ref="N8:R8"/>
+    <mergeCell ref="S8:X8"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="E9:M9"/>
     <mergeCell ref="N9:R9"/>
-    <mergeCell ref="E8:M8"/>
-    <mergeCell ref="N8:R8"/>
-    <mergeCell ref="A14:X14"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="S9:X9"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="N10:X10"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="N11:X11"/>
+    <mergeCell ref="A12:M13"/>
+    <mergeCell ref="N12:X13"/>
+    <mergeCell ref="A14:X14"/>
+    <mergeCell ref="A15:X20"/>
   </mergeCells>
-  <phoneticPr fontId="17" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="Z2:Z37" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="Z10:Z37">
+      <formula1>"머리말,꼬리말,열머리,그룹머리,반복,그룹꼬리,합계"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="Z2:Z37">
       <formula1>"머리말,꼬리말,열머리,그룹머리,반복,그룹꼬리,합계"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="17" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1985,490 +2042,494 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="12" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" ht="15" customHeight="1" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="62" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="13" customFormat="1" ht="14" customHeight="1">
-      <c r="A2" s="11" t="s">
+    <row r="2" ht="14" customHeight="1" spans="1:5" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11" t="s">
+      <c r="B2" s="60"/>
+      <c r="C2" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-    </row>
-    <row r="3" spans="1:5" ht="20" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="11"/>
-    </row>
-    <row r="4" spans="1:5" ht="20" customHeight="1">
-      <c r="A4" s="11" t="s">
+      <c r="E3" s="60"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-    </row>
-    <row r="5" spans="1:5" ht="20" customHeight="1">
-      <c r="A5" s="11" t="s">
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-    </row>
-    <row r="6" spans="1:5" ht="20" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-    </row>
-    <row r="7" spans="1:5" ht="20" customHeight="1">
-      <c r="A7" s="11" t="s">
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="11"/>
-    </row>
-    <row r="8" spans="1:5" ht="20" customHeight="1">
-      <c r="A8" s="11" t="s">
+      <c r="E7" s="60"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-    </row>
-    <row r="9" spans="1:5" ht="20" customHeight="1">
-      <c r="A9" s="11" t="s">
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="11"/>
-    </row>
-    <row r="10" spans="1:5" ht="20" customHeight="1">
-      <c r="A10" s="11" t="s">
+      <c r="E9" s="60"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-    </row>
-    <row r="11" spans="1:5" ht="20" customHeight="1">
-      <c r="A11" s="11" t="s">
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-    </row>
-    <row r="12" spans="1:5" ht="20" customHeight="1">
-      <c r="A12" s="11" t="s">
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11" t="s">
+      <c r="D12" s="60"/>
+      <c r="E12" s="60" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="20" customHeight="1">
-      <c r="A13" s="11" t="s">
+    <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="60" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="20" customHeight="1">
-      <c r="A14" s="11" t="s">
+    <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11" t="s">
+      <c r="D14" s="60"/>
+      <c r="E14" s="60" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="20" customHeight="1">
-      <c r="A15" s="11" t="s">
+    <row r="15" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11" t="s">
+      <c r="D15" s="60"/>
+      <c r="E15" s="60" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="20" customHeight="1"/>
-    <row r="17" ht="20" customHeight="1"/>
-    <row r="18" ht="20" customHeight="1"/>
-    <row r="19" ht="20" customHeight="1"/>
-    <row r="20" ht="20" customHeight="1"/>
-    <row r="21" ht="20" customHeight="1"/>
-    <row r="22" ht="20" customHeight="1"/>
-    <row r="23" ht="20" customHeight="1"/>
-    <row r="24" ht="20" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1"/>
-    <row r="26" ht="20" customHeight="1"/>
-    <row r="27" ht="20" customHeight="1"/>
-    <row r="28" ht="20" customHeight="1"/>
-    <row r="29" ht="20" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1"/>
-    <row r="31" ht="20" customHeight="1"/>
-    <row r="32" ht="20" customHeight="1"/>
-    <row r="33" ht="20" customHeight="1"/>
-    <row r="34" ht="20" customHeight="1"/>
-    <row r="35" ht="20" customHeight="1"/>
-    <row r="36" ht="20" customHeight="1"/>
-    <row r="37" ht="20" customHeight="1"/>
-    <row r="38" ht="20" customHeight="1"/>
-    <row r="39" ht="20" customHeight="1"/>
-    <row r="40" ht="20" customHeight="1"/>
-    <row r="41" ht="20" customHeight="1"/>
-    <row r="42" ht="20" customHeight="1"/>
-    <row r="43" ht="20" customHeight="1"/>
-    <row r="44" ht="20" customHeight="1"/>
-    <row r="45" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C76" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" sqref="C10:C76">
       <formula1>"글자,숫자,금액,날짜,여러 줄,선택,예아니오,이미지"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D76" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C76">
+      <formula1>"글자,숫자,금액,날짜,여러 줄,선택,예아니오,이미지"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D76">
+      <formula1>"필수"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D2:D76">
       <formula1>"필수"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="17" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="14" customFormat="1" ht="34.75" customHeight="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" ht="34.75" customHeight="1" spans="1:2" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="64" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A2" s="15" t="s">
+    <row r="2" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="65" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A3" s="15" t="s">
+    <row r="3" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="65" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A4" s="15" t="s">
+    <row r="4" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="65" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="14" customFormat="1" ht="34.75" customHeight="1">
-      <c r="A5" s="14" t="s">
+    <row r="5" ht="34.75" customHeight="1" spans="1:2" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="64" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A6" s="15" t="s">
+    <row r="6" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="65" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A7" s="15" t="s">
+    <row r="7" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="65" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A8" s="15" t="s">
+    <row r="8" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="65" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="14" customFormat="1" ht="34.75" customHeight="1">
-      <c r="A9" s="14" t="s">
+    <row r="9" ht="34.75" customHeight="1" spans="1:2" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="64" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A10" s="15" t="s">
+    <row r="10" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="65" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A11" s="15" t="s">
+    <row r="11" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="65" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A12" s="15" t="s">
+    <row r="12" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="65" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A13" s="15" t="s">
+    <row r="13" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="65" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A14" s="15" t="s">
+    <row r="14" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="65" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:2" s="14" customFormat="1" ht="34.75" customHeight="1">
-      <c r="A15" s="14" t="s">
+    <row r="15" ht="34.75" customHeight="1" spans="1:2" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="64" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A16" s="15" t="s">
+    <row r="16" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="65" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A17" s="15" t="s">
+    <row r="17" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="65" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A18" s="15" t="s">
+    <row r="18" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="65" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A19" s="15" t="s">
+    <row r="19" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="65" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A20" s="15" t="s">
+    <row r="20" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="65" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A21" s="15" t="s">
+    <row r="21" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="65" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="14" customFormat="1" ht="34.75" customHeight="1">
-      <c r="A22" s="14" t="s">
+    <row r="22" ht="34.75" customHeight="1" spans="1:2" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="64" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A23" s="15" t="s">
+    <row r="23" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="65" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A24" s="15" t="s">
+    <row r="24" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="65" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A25" s="15" t="s">
+    <row r="25" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="65" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A26" s="15" t="s">
+    <row r="26" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="65" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:2" s="15" customFormat="1" ht="24" customHeight="1">
-      <c r="A27" s="15" t="s">
+    <row r="27" ht="24" customHeight="1" spans="1:2" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="65" t="s">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>